--- a/example-spreadsheets/study-tasks/task-03/task03_inventoryPricing.xlsx
+++ b/example-spreadsheets/study-tasks/task-03/task03_inventoryPricing.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t xml:space="preserve">Task 3</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t xml:space="preserve">Explain in your words what the formula in  D3 is doing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now based on the recommendation lower the price of the product to 30$.</t>
   </si>
 </sst>
 </file>
@@ -265,10 +268,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -282,6 +281,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -415,9 +418,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -434,69 +437,69 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -543,61 +546,61 @@
       <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="4" t="n">
         <v>45658</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>45658</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>45627</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>45658</v>
       </c>
     </row>
@@ -617,36 +620,36 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="1"/>
       <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
       <c r="J1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="2"/>
+      <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -688,87 +691,95 @@
       <c r="M2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="N2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="str">
+      <c r="B3" s="2" t="str">
         <f aca="false">VLOOKUP(A3,Product_Catalog!A4:B7,2,0)</f>
         <v>Gadget</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="2" t="n">
         <f aca="false">VLOOKUP(A3,Product_Catalog!A4:C7,3,0)</f>
         <v>48</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="2" t="n">
         <f aca="false">VLOOKUP(A3,Supplier_Costs!A3:C6,3,0)</f>
         <v>28</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="2" t="n">
         <f aca="false">D3*(1+E3)</f>
         <v>42</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="2" t="n">
         <f aca="false">C3-D3</f>
         <v>20</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="2" t="n">
         <f aca="false">G3/D3%</f>
         <v>71.4285714285714</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="2" t="n">
         <f aca="false">G3</f>
         <v>20</v>
       </c>
-      <c r="J3" s="3" t="str">
+      <c r="J3" s="2" t="str">
         <f aca="false">IF(C3&gt;=F3, "Above", "Below")</f>
         <v>Above</v>
       </c>
-      <c r="K3" s="3" t="str">
+      <c r="K3" s="2" t="str">
         <f aca="false">IF(J3="Above", "APPROVED", "NEEDS REVIEW")</f>
         <v>APPROVED</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="2" t="n">
         <f aca="false">F3*0.95</f>
         <v>39.9</v>
       </c>
-      <c r="M3" s="3" t="str">
+      <c r="M3" s="2" t="str">
         <f aca="false">IF(C3&gt;L3, "Lower Price", "Price OK")</f>
         <v>Lower Price</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="6" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
